--- a/Builder + Caller Masterlist - SBC 2026.xlsx
+++ b/Builder + Caller Masterlist - SBC 2026.xlsx
@@ -5068,7 +5068,7 @@
     <row r="67" ht="48" customHeight="1" s="47">
       <c r="A67" s="49" t="inlineStr">
         <is>
-          <t>Beach Electrical</t>
+          <t>Beach Electrical LLC (dba Beach Electric)</t>
         </is>
       </c>
       <c r="B67" s="49" t="inlineStr">
@@ -5078,47 +5078,47 @@
       </c>
       <c r="C67" s="49" t="inlineStr">
         <is>
-          <t>Felton, CA (Santa Cruz; serves South Bay)</t>
+          <t>Felton, CA (Santa Cruz; advertises San Jose / Bay Area work)</t>
         </is>
       </c>
       <c r="D67" s="49" t="inlineStr">
         <is>
+          <t>Jason Beach (Jason Lee Beach)</t>
+        </is>
+      </c>
+      <c r="E67" s="50" t="inlineStr">
+        <is>
+          <t>(831) 246-4014</t>
+        </is>
+      </c>
+      <c r="F67" s="49" t="inlineStr">
+        <is>
+          <t>Owner Direct</t>
+        </is>
+      </c>
+      <c r="G67" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="H67" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E67" s="50" t="inlineStr">
-        <is>
-          <t>(831) 246-4014</t>
-        </is>
-      </c>
-      <c r="F67" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G67" s="49" t="n">
-        <v>30</v>
-      </c>
-      <c r="H67" s="49" t="inlineStr">
+      <c r="I67" s="49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J67" s="49" t="inlineStr">
+        <is>
+          <t>https://beachelectricalca.com/services/lightning-protection-system/</t>
+        </is>
+      </c>
+      <c r="K67" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="I67" s="49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J67" s="49" t="inlineStr">
-        <is>
-          <t>https://beachelectricalca.com/services/lightning-protection-system/</t>
-        </is>
-      </c>
-      <c r="K67" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="L67" s="49" t="inlineStr">
         <is>
           <t>New</t>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="M67" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the current owner. C-10 electricians advertising NFPA 780 lightning-protection system design/install (air terminals, conductors, ground rods). Santa Cruz County — confirm Bay Area job mix.</t>
+          <t>Owner-direct contact is published for Jason Beach; confirm they are still the current equity owner. Closest local NFPA 780 lightning-protection installer (air terminals, conductors, ground rods, panel SPD). CSLB C-10 #1108407. LLC formed 2022; owner cites 30+ years electrical experience. Alt (408) 310-9447.</t>
         </is>
       </c>
       <c r="N67" s="49" t="inlineStr">
@@ -5143,7 +5143,7 @@
     <row r="68" ht="48" customHeight="1" s="47">
       <c r="A68" s="49" t="inlineStr">
         <is>
-          <t>Skyline Electric LLC</t>
+          <t>Bravo Communications, Inc.</t>
         </is>
       </c>
       <c r="B68" s="49" t="inlineStr">
@@ -5153,47 +5153,47 @@
       </c>
       <c r="C68" s="49" t="inlineStr">
         <is>
-          <t>Hayward, CA (Alameda)</t>
+          <t>San Jose, CA (Santa Clara)</t>
         </is>
       </c>
       <c r="D68" s="49" t="inlineStr">
         <is>
+          <t>Dennis L. Mozingo</t>
+        </is>
+      </c>
+      <c r="E68" s="50" t="inlineStr">
+        <is>
+          <t>(408) 297-8700</t>
+        </is>
+      </c>
+      <c r="F68" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G68" s="49" t="n">
+        <v>41</v>
+      </c>
+      <c r="H68" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E68" s="50" t="inlineStr">
-        <is>
-          <t>(510) 470-0520</t>
-        </is>
-      </c>
-      <c r="F68" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G68" s="49" t="n">
-        <v>10</v>
-      </c>
-      <c r="H68" s="49" t="inlineStr">
+      <c r="I68" s="49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J68" s="49" t="inlineStr">
+        <is>
+          <t>http://www.bravobravo.com</t>
+        </is>
+      </c>
+      <c r="K68" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="I68" s="49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J68" s="49" t="inlineStr">
-        <is>
-          <t>https://www.skylineelectricusa.com/whole-house-surge-protection</t>
-        </is>
-      </c>
-      <c r="K68" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="L68" s="49" t="inlineStr">
         <is>
           <t>New</t>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="M68" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the current owner. Advertises whole-house surge protection, panel SPD integration, and grounding/bonding. CSLB C-10 #1121036; alt (510) 512-5362. 22263 Prospect St.</t>
+          <t>Business line: ask for Dennis L. Mozingo and confirm current ownership. San Jose manufacturer/supplier of lightning and surge-protection products (Sure/Fire) plus consulting. Founded 1985. Product/consulting fit, not a typical field LPS installer. Alt (408) 270-1547.</t>
         </is>
       </c>
       <c r="N68" s="49" t="inlineStr">
@@ -5218,7 +5218,7 @@
     <row r="69" ht="48" customHeight="1" s="47">
       <c r="A69" s="49" t="inlineStr">
         <is>
-          <t>Frayer Electric Inc.</t>
+          <t>Yotta Electrical Services, Inc.</t>
         </is>
       </c>
       <c r="B69" s="49" t="inlineStr">
@@ -5228,34 +5228,32 @@
       </c>
       <c r="C69" s="49" t="inlineStr">
         <is>
-          <t>East Bay / Patterson service area, CA</t>
+          <t>San Jose, CA (Santa Clara)</t>
         </is>
       </c>
       <c r="D69" s="49" t="inlineStr">
         <is>
+          <t>Thomas Burg (CEO); Leon Badarie also listed as co-founder in some profiles</t>
+        </is>
+      </c>
+      <c r="E69" s="50" t="inlineStr">
+        <is>
+          <t>(408) 256-7653</t>
+        </is>
+      </c>
+      <c r="F69" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G69" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="H69" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E69" s="50" t="inlineStr">
-        <is>
-          <t>(510) 861-6247</t>
-        </is>
-      </c>
-      <c r="F69" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G69" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="H69" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="I69" s="49" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -5263,12 +5261,12 @@
       </c>
       <c r="J69" s="49" t="inlineStr">
         <is>
-          <t>https://frayerelectricinc.com/services/whole-house-surge-protection/</t>
+          <t>https://yottaelectric.com/</t>
         </is>
       </c>
       <c r="K69" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>info@yottaelectric.com</t>
         </is>
       </c>
       <c r="L69" s="49" t="inlineStr">
@@ -5278,7 +5276,7 @@
       </c>
       <c r="M69" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the current owner. C-10 #1101008; locally owned; advertises whole-house SPD install and grounding. Confirm primary operating city and commercial mix.</t>
+          <t>Business line: ask for Thomas Burg and confirm current ownership. Dedicated commercial surge-protection and grounding-system design/install page. Started Dec 2018. SCVNECA also lists Tom Burg (408) 205-6478 / tom@yottaelectric.com.</t>
         </is>
       </c>
       <c r="N69" s="49" t="inlineStr">
@@ -5295,7 +5293,7 @@
     <row r="70" ht="48" customHeight="1" s="47">
       <c r="A70" s="49" t="inlineStr">
         <is>
-          <t>Eleos Electric</t>
+          <t>Towery Electric, Inc.</t>
         </is>
       </c>
       <c r="B70" s="49" t="inlineStr">
@@ -5305,49 +5303,47 @@
       </c>
       <c r="C70" s="49" t="inlineStr">
         <is>
-          <t>Windsor / Santa Rosa, CA (Sonoma)</t>
+          <t>Novato, CA (Marin)</t>
         </is>
       </c>
       <c r="D70" s="49" t="inlineStr">
         <is>
+          <t>Alex Towery</t>
+        </is>
+      </c>
+      <c r="E70" s="50" t="inlineStr">
+        <is>
+          <t>(415) 419-5960</t>
+        </is>
+      </c>
+      <c r="F70" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G70" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="H70" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E70" s="50" t="inlineStr">
-        <is>
-          <t>(707) 837-6722</t>
-        </is>
-      </c>
-      <c r="F70" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G70" s="49" t="inlineStr">
+      <c r="I70" s="49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J70" s="49" t="inlineStr">
+        <is>
+          <t>https://toweryelectric.com/</t>
+        </is>
+      </c>
+      <c r="K70" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="H70" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="I70" s="49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J70" s="49" t="inlineStr">
-        <is>
-          <t>https://eleoselectric.com/surge-protection-installation</t>
-        </is>
-      </c>
-      <c r="K70" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="L70" s="49" t="inlineStr">
         <is>
           <t>New</t>
@@ -5355,7 +5351,7 @@
       </c>
       <c r="M70" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the current owner. Advertises Type 1/Type 2 whole-home surge protection for lightning, PSPS restoration, and grid spikes across Sonoma County.</t>
+          <t>Business line: ask for Alex Towery and confirm current ownership. Dedicated Type 1/Type 2 whole-house surge-protection page, including grounding/bonding. Founded 2014; CSLB C-10 #989290. 46 Digital Dr, Ste 1.</t>
         </is>
       </c>
       <c r="N70" s="49" t="inlineStr">
@@ -5372,7 +5368,7 @@
     <row r="71" ht="48" customHeight="1" s="47">
       <c r="A71" s="49" t="inlineStr">
         <is>
-          <t>Wendt Electric Inc.</t>
+          <t>Infinium Solar, Roofing and Electric</t>
         </is>
       </c>
       <c r="B71" s="49" t="inlineStr">
@@ -5382,17 +5378,17 @@
       </c>
       <c r="C71" s="49" t="inlineStr">
         <is>
-          <t>Sebastopol, CA (Sonoma)</t>
+          <t>Campbell, CA (Santa Clara)</t>
         </is>
       </c>
       <c r="D71" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>Jeff L. (Yelp owner listing; surname not fully verified)</t>
         </is>
       </c>
       <c r="E71" s="50" t="inlineStr">
         <is>
-          <t>(707) 953-2582</t>
+          <t>(408) 583-8101</t>
         </is>
       </c>
       <c r="F71" s="49" t="inlineStr">
@@ -5400,13 +5396,11 @@
           <t>Business Line</t>
         </is>
       </c>
-      <c r="G71" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
+      <c r="G71" s="49" t="n">
+        <v>18</v>
       </c>
       <c r="H71" s="49" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I71" s="49" t="inlineStr">
         <is>
@@ -5415,12 +5409,12 @@
       </c>
       <c r="J71" s="49" t="inlineStr">
         <is>
-          <t>https://wendtelectric68.com/surge-protection/</t>
+          <t>https://infinium.inc/electrical/surge-protection/</t>
         </is>
       </c>
       <c r="K71" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>contact@infiniumsolar.com</t>
         </is>
       </c>
       <c r="L71" s="49" t="inlineStr">
@@ -5430,7 +5424,7 @@
       </c>
       <c r="M71" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the current owner. Advertises whole-house and commercial surge protection (Leviton, Square D, Eaton). 2235 Schaeffer Rd; ~10–50 employees.</t>
+          <t>Business line: ask for Jeff and confirm current ownership. Dedicated whole-house surge-protection page. Founded 2008; CSLB #1031953. Pleasanton line (925) 401-7320. Solar/roofing/electrical contractor, not a lightning-rod specialist.</t>
         </is>
       </c>
       <c r="N71" s="49" t="inlineStr">
@@ -5447,7 +5441,7 @@
     <row r="72" ht="48" customHeight="1" s="47">
       <c r="A72" s="49" t="inlineStr">
         <is>
-          <t>YKCA Electric</t>
+          <t>Guerreros Electric, Inc.</t>
         </is>
       </c>
       <c r="B72" s="49" t="inlineStr">
@@ -5457,34 +5451,32 @@
       </c>
       <c r="C72" s="49" t="inlineStr">
         <is>
-          <t>San Carlos, CA (San Mateo)</t>
+          <t>Berkeley, CA (Alameda)</t>
         </is>
       </c>
       <c r="D72" s="49" t="inlineStr">
         <is>
+          <t>Juan Carlos Guerrero</t>
+        </is>
+      </c>
+      <c r="E72" s="50" t="inlineStr">
+        <is>
+          <t>(510) 409-3627</t>
+        </is>
+      </c>
+      <c r="F72" s="49" t="inlineStr">
+        <is>
+          <t>Owner Direct</t>
+        </is>
+      </c>
+      <c r="G72" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="H72" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E72" s="50" t="inlineStr">
-        <is>
-          <t>(650) 550-0819</t>
-        </is>
-      </c>
-      <c r="F72" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G72" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="H72" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="I72" s="49" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -5492,12 +5484,12 @@
       </c>
       <c r="J72" s="49" t="inlineStr">
         <is>
-          <t>https://ykca.com/</t>
+          <t>https://www.guerreroselectric.com/surge-protection</t>
         </is>
       </c>
       <c r="K72" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>carlos@guerreroselectric.com</t>
         </is>
       </c>
       <c r="L72" s="49" t="inlineStr">
@@ -5507,7 +5499,7 @@
       </c>
       <c r="M72" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the current owner. Licensed C-10 &amp; B contractor serving the Peninsula. Surge/lightning is referenced in terms; confirm they actively sell lightning/surge installs before a fit discussion.</t>
+          <t>Owner-direct contact is published for Juan Carlos Guerrero; confirm they are still the current equity owner. Dedicated full-home surge-protection page. CA corp filed 2014. 2127 6th St, Berkeley.</t>
         </is>
       </c>
       <c r="N72" s="49" t="inlineStr">
@@ -5524,7 +5516,7 @@
     <row r="73" ht="48" customHeight="1" s="47">
       <c r="A73" s="49" t="inlineStr">
         <is>
-          <t>Quality Electrical Solution (QES)</t>
+          <t>Eleos Electric (John Evans Enterprises, Inc.)</t>
         </is>
       </c>
       <c r="B73" s="49" t="inlineStr">
@@ -5534,49 +5526,47 @@
       </c>
       <c r="C73" s="49" t="inlineStr">
         <is>
-          <t>Concord, CA (Contra Costa)</t>
+          <t>Windsor, CA (Sonoma)</t>
         </is>
       </c>
       <c r="D73" s="49" t="inlineStr">
         <is>
+          <t>John Evans</t>
+        </is>
+      </c>
+      <c r="E73" s="50" t="inlineStr">
+        <is>
+          <t>(707) 837-6722</t>
+        </is>
+      </c>
+      <c r="F73" s="49" t="inlineStr">
+        <is>
+          <t>Owner Direct</t>
+        </is>
+      </c>
+      <c r="G73" s="49" t="n">
+        <v>36</v>
+      </c>
+      <c r="H73" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E73" s="50" t="inlineStr">
+      <c r="I73" s="49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J73" s="49" t="inlineStr">
+        <is>
+          <t>https://eleoselectric.com/surge-protection-installation</t>
+        </is>
+      </c>
+      <c r="K73" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="F73" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G73" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="H73" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="I73" s="49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J73" s="49" t="inlineStr">
-        <is>
-          <t>https://www.go-qes.com/service-areas/concord-electrical-services</t>
-        </is>
-      </c>
-      <c r="K73" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="L73" s="49" t="inlineStr">
         <is>
           <t>New</t>
@@ -5584,7 +5574,7 @@
       </c>
       <c r="M73" s="49" t="inlineStr">
         <is>
-          <t>Ask for the current owner. Licensed C-10 serving Concord/Hwy 4–I-680; commercial and residential electrical. Confirm explicit surge/lightning-protection offering and a published phone on the call.</t>
+          <t>Owner-direct: site says the owner usually answers; confirm John Evans is still the current equity owner. Type 1/Type 2 whole-home SPDs for lightning, PSPS, and grid spikes. CSLB #1009044. 930 Shiloh Rd, Bldg 41, Ste C.</t>
         </is>
       </c>
       <c r="N73" s="49" t="inlineStr">
@@ -5601,7 +5591,7 @@
     <row r="74" ht="48" customHeight="1" s="47">
       <c r="A74" s="49" t="inlineStr">
         <is>
-          <t>Ongaro &amp; Sons</t>
+          <t>Skyline Electric LLC</t>
         </is>
       </c>
       <c r="B74" s="49" t="inlineStr">
@@ -5611,49 +5601,47 @@
       </c>
       <c r="C74" s="49" t="inlineStr">
         <is>
-          <t>Napa / North Bay, CA</t>
+          <t>Hayward, CA (Alameda)</t>
         </is>
       </c>
       <c r="D74" s="49" t="inlineStr">
         <is>
-          <t>Ongaro family</t>
+          <t>Eduard Sandulyak</t>
         </is>
       </c>
       <c r="E74" s="50" t="inlineStr">
         <is>
-          <t>(415) 741-2820</t>
+          <t>(510) 470-0520</t>
         </is>
       </c>
       <c r="F74" s="49" t="inlineStr">
         <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G74" s="49" t="inlineStr">
+          <t>Owner Direct</t>
+        </is>
+      </c>
+      <c r="G74" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="H74" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="H74" s="49" t="inlineStr">
+      <c r="I74" s="49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J74" s="49" t="inlineStr">
+        <is>
+          <t>https://www.skylineelectricusa.com/whole-house-surge-protection</t>
+        </is>
+      </c>
+      <c r="K74" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="I74" s="49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J74" s="49" t="inlineStr">
-        <is>
-          <t>https://ongaroandsons.com/service-area/napa-ca/</t>
-        </is>
-      </c>
-      <c r="K74" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="L74" s="49" t="inlineStr">
         <is>
           <t>New</t>
@@ -5661,7 +5649,7 @@
       </c>
       <c r="M74" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the Ongaro family and confirm current ownership. Licensed electrical (plus HVAC/plumbing) serving Napa. Confirm they install surge/lightning-protection systems, not only general electrical.</t>
+          <t>Owner-direct contact is published for Eduard Sandulyak; confirm they are still the current equity owner. Whole-house surge plus grounding/bonding. LLC filed 2023; CSLB C-10 #1121036. 22263 Prospect St. Screening: public entity is about 3 years old.</t>
         </is>
       </c>
       <c r="N74" s="49" t="inlineStr">
@@ -5678,7 +5666,7 @@
     <row r="75" ht="48" customHeight="1" s="47">
       <c r="A75" s="49" t="inlineStr">
         <is>
-          <t>J&amp;J Electric, Inc.</t>
+          <t>Avant Electric, Inc.</t>
         </is>
       </c>
       <c r="B75" s="49" t="inlineStr">
@@ -5688,34 +5676,32 @@
       </c>
       <c r="C75" s="49" t="inlineStr">
         <is>
-          <t>Santa Rosa, CA (Sonoma)</t>
+          <t>Santa Clara, CA (Santa Clara)</t>
         </is>
       </c>
       <c r="D75" s="49" t="inlineStr">
         <is>
+          <t>Brian Gerlach (owner; firm also described as woman-owned)</t>
+        </is>
+      </c>
+      <c r="E75" s="50" t="inlineStr">
+        <is>
+          <t>(408) 688-1546</t>
+        </is>
+      </c>
+      <c r="F75" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G75" s="49" t="n">
+        <v>35</v>
+      </c>
+      <c r="H75" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E75" s="50" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="F75" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G75" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="H75" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="I75" s="49" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -5723,12 +5709,12 @@
       </c>
       <c r="J75" s="49" t="inlineStr">
         <is>
-          <t>https://jjelectricco.com/</t>
+          <t>https://avant-electric.com/electrician/ground-wire-installation/</t>
         </is>
       </c>
       <c r="K75" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>avant@avant-electric.com</t>
         </is>
       </c>
       <c r="L75" s="49" t="inlineStr">
@@ -5738,7 +5724,7 @@
       </c>
       <c r="M75" s="49" t="inlineStr">
         <is>
-          <t>Ask for the current owner. C-10 contractor for Sonoma, Napa, and Marin residential/commercial electrical. Confirm surge/lightning-protection offering and published phone on the call.</t>
+          <t>Business line: ask for Brian Gerlach and confirm current ownership. Explicit grounding-system and whole-home surge pages. 2066 A Walsh Ave. Diamond Certified owner line (408) 874-6906.</t>
         </is>
       </c>
       <c r="N75" s="49" t="inlineStr">
@@ -5755,7 +5741,7 @@
     <row r="76" ht="48" customHeight="1" s="47">
       <c r="A76" s="49" t="inlineStr">
         <is>
-          <t>Wilson Electric</t>
+          <t>Dollens Electric Corporation</t>
         </is>
       </c>
       <c r="B76" s="49" t="inlineStr">
@@ -5765,49 +5751,47 @@
       </c>
       <c r="C76" s="49" t="inlineStr">
         <is>
-          <t>San Mateo / Santa Cruz / Santa Clara counties, CA</t>
+          <t>San Jose, CA (Santa Clara)</t>
         </is>
       </c>
       <c r="D76" s="49" t="inlineStr">
         <is>
+          <t>Jason Dollens (President); Josephine Dollens also listed on BBB</t>
+        </is>
+      </c>
+      <c r="E76" s="50" t="inlineStr">
+        <is>
+          <t>(408) 929-6100</t>
+        </is>
+      </c>
+      <c r="F76" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G76" s="49" t="n">
+        <v>21</v>
+      </c>
+      <c r="H76" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E76" s="50" t="inlineStr">
-        <is>
-          <t>(888) 967-5791</t>
-        </is>
-      </c>
-      <c r="F76" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G76" s="49" t="inlineStr">
+      <c r="I76" s="49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J76" s="49" t="inlineStr">
+        <is>
+          <t>https://dollenselectric.com/whole-house-surge-protector-installation/</t>
+        </is>
+      </c>
+      <c r="K76" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="H76" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="I76" s="49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J76" s="49" t="inlineStr">
-        <is>
-          <t>https://wilsonelectric.works/</t>
-        </is>
-      </c>
-      <c r="K76" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="L76" s="49" t="inlineStr">
         <is>
           <t>New</t>
@@ -5815,7 +5799,7 @@
       </c>
       <c r="M76" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the current owner. Bay Area residential electrical contractor. Confirm they actively sell surge or lightning-protection systems versus general wiring only.</t>
+          <t>Business line: ask for Jason Dollens and confirm current ownership. Dedicated San Jose whole-house surge-protector page. Family-owned; BBB founding 2004. 3240 S White Rd.</t>
         </is>
       </c>
       <c r="N76" s="49" t="inlineStr">
@@ -5832,7 +5816,7 @@
     <row r="77" ht="48" customHeight="1" s="47">
       <c r="A77" s="49" t="inlineStr">
         <is>
-          <t>JJC Electric</t>
+          <t>Arsen Electric Inc.</t>
         </is>
       </c>
       <c r="B77" s="49" t="inlineStr">
@@ -5842,49 +5826,47 @@
       </c>
       <c r="C77" s="49" t="inlineStr">
         <is>
-          <t>Fremont, CA (Alameda)</t>
+          <t>San Jose / Sunnyvale, CA (Santa Clara)</t>
         </is>
       </c>
       <c r="D77" s="49" t="inlineStr">
         <is>
+          <t>Dmitry Druzhina</t>
+        </is>
+      </c>
+      <c r="E77" s="50" t="inlineStr">
+        <is>
+          <t>(408) 594-9770</t>
+        </is>
+      </c>
+      <c r="F77" s="49" t="inlineStr">
+        <is>
+          <t>Owner Direct</t>
+        </is>
+      </c>
+      <c r="G77" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="H77" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E77" s="50" t="inlineStr">
-        <is>
-          <t>(866) 740-1093</t>
-        </is>
-      </c>
-      <c r="F77" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G77" s="49" t="inlineStr">
+      <c r="I77" s="49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J77" s="49" t="inlineStr">
+        <is>
+          <t>https://arsenelectric.com/</t>
+        </is>
+      </c>
+      <c r="K77" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="H77" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="I77" s="49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J77" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="K77" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="L77" s="49" t="inlineStr">
         <is>
           <t>New</t>
@@ -5892,7 +5874,7 @@
       </c>
       <c r="M77" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the current owner. Public listings describe a Fremont electrician offering whole-house surge protection. Verify legal name, website, and that this is not a lead-gen listing.</t>
+          <t>Owner-direct contact is published for Dmitry Druzhina; confirm they are still the current equity owner. Lists surge protection among core services. Serving Bay Area since 2017; CSLB #1034404.</t>
         </is>
       </c>
       <c r="N77" s="49" t="inlineStr">
@@ -5909,7 +5891,7 @@
     <row r="78" ht="48" customHeight="1" s="47">
       <c r="A78" s="49" t="inlineStr">
         <is>
-          <t>SFE Electric Inc.</t>
+          <t>Rocky Hill Electric Inc.</t>
         </is>
       </c>
       <c r="B78" s="49" t="inlineStr">
@@ -5919,47 +5901,45 @@
       </c>
       <c r="C78" s="49" t="inlineStr">
         <is>
-          <t>Concord, CA (Contra Costa)</t>
+          <t>San Rafael, CA (Marin)</t>
         </is>
       </c>
       <c r="D78" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified (family-owned; CEO listed on LinkedIn)</t>
+          <t>Bengiamino (Ben) E. Ielmorini</t>
         </is>
       </c>
       <c r="E78" s="50" t="inlineStr">
         <is>
+          <t>(415) 523-5201</t>
+        </is>
+      </c>
+      <c r="F78" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G78" s="49" t="n">
+        <v>7</v>
+      </c>
+      <c r="H78" s="49" t="n">
+        <v>7</v>
+      </c>
+      <c r="I78" s="49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J78" s="49" t="inlineStr">
+        <is>
+          <t>https://www.rockyhillelectric.com/home-surge-protection-in-san-rafael-ca-why-every-modern-home-needs-it/</t>
+        </is>
+      </c>
+      <c r="K78" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="F78" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G78" s="49" t="n">
-        <v>10</v>
-      </c>
-      <c r="H78" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="I78" s="49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J78" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="K78" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="L78" s="49" t="inlineStr">
         <is>
           <t>New</t>
@@ -5967,7 +5947,7 @@
       </c>
       <c r="M78" s="49" t="inlineStr">
         <is>
-          <t>Ask for the current owner/CEO. Family-owned East Bay electrical firm (panel upgrades, commercial/residential). Confirm surge/lightning offering and a working business line.</t>
+          <t>Business line: ask for Ben Ielmorini and confirm current ownership. Explicit Type 1/Type 2 panel SPD and grounding/bonding content. Founded 2019. 4330 Redwood Hwy, Ste 200. Owner has described a 7-technician team.</t>
         </is>
       </c>
       <c r="N78" s="49" t="inlineStr">
@@ -5984,7 +5964,7 @@
     <row r="79" ht="48" customHeight="1" s="47">
       <c r="A79" s="49" t="inlineStr">
         <is>
-          <t>VFC Lightning Protection — California / Western region</t>
+          <t>Divine Electric and Plumbing</t>
         </is>
       </c>
       <c r="B79" s="49" t="inlineStr">
@@ -5994,45 +5974,45 @@
       </c>
       <c r="C79" s="49" t="inlineStr">
         <is>
-          <t>Serves Bay Area projects; CA division in Ontario (SoCal)</t>
+          <t>San Rafael, CA (Marin)</t>
         </is>
       </c>
       <c r="D79" s="49" t="inlineStr">
         <is>
+          <t>Darin Divine</t>
+        </is>
+      </c>
+      <c r="E79" s="50" t="inlineStr">
+        <is>
+          <t>(415) 213-4972</t>
+        </is>
+      </c>
+      <c r="F79" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G79" s="49" t="n">
+        <v>23</v>
+      </c>
+      <c r="H79" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="I79" s="49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J79" s="49" t="inlineStr">
+        <is>
+          <t>https://www.calldivine.com/electrical-services/home-surge-protection/</t>
+        </is>
+      </c>
+      <c r="K79" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E79" s="50" t="inlineStr">
-        <is>
-          <t>(800) 825-1948</t>
-        </is>
-      </c>
-      <c r="F79" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G79" s="49" t="n">
-        <v>37</v>
-      </c>
-      <c r="H79" s="49" t="n">
-        <v>45</v>
-      </c>
-      <c r="I79" s="49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J79" s="49" t="inlineStr">
-        <is>
-          <t>https://vfclp.com/</t>
-        </is>
-      </c>
-      <c r="K79" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="L79" s="49" t="inlineStr">
         <is>
           <t>New</t>
@@ -6040,7 +6020,7 @@
       </c>
       <c r="M79" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the Western regional manager. Pure-play LPI lightning-protection contractor (est. ~1989) that staffs Bay Area projects. Confirm a local decision-maker; HQ is North Salt Lake, UT.</t>
+          <t>Business line: ask for Darin Divine and confirm current ownership. Dedicated Marin whole-house surge-protection page. Founded 2003; CSLB #817357 (C-10/C-36). 2935 Kerner Blvd, Ste E.</t>
         </is>
       </c>
       <c r="N79" s="49" t="inlineStr">
@@ -6057,7 +6037,7 @@
     <row r="80" ht="48" customHeight="1" s="47">
       <c r="A80" s="49" t="inlineStr">
         <is>
-          <t>Kuefler Lightning Protection (distributor)</t>
+          <t>Owens Electric &amp; Solar</t>
         </is>
       </c>
       <c r="B80" s="49" t="inlineStr">
@@ -6067,49 +6047,45 @@
       </c>
       <c r="C80" s="49" t="inlineStr">
         <is>
-          <t>Serves California statewide</t>
+          <t>San Mateo, CA (San Mateo)</t>
         </is>
       </c>
       <c r="D80" s="49" t="inlineStr">
         <is>
+          <t>Jeff Owens</t>
+        </is>
+      </c>
+      <c r="E80" s="50" t="inlineStr">
+        <is>
+          <t>(650) 348-5727</t>
+        </is>
+      </c>
+      <c r="F80" s="49" t="inlineStr">
+        <is>
+          <t>Owner Direct</t>
+        </is>
+      </c>
+      <c r="G80" s="49" t="n">
+        <v>61</v>
+      </c>
+      <c r="H80" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="I80" s="49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J80" s="49" t="inlineStr">
+        <is>
+          <t>https://www.owenselectricinc.com/electrical/surge-protection</t>
+        </is>
+      </c>
+      <c r="K80" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E80" s="50" t="inlineStr">
-        <is>
-          <t>(800) 370-5886</t>
-        </is>
-      </c>
-      <c r="F80" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G80" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="H80" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="I80" s="49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J80" s="49" t="inlineStr">
-        <is>
-          <t>https://kuefler-lightning.com/states/california/</t>
-        </is>
-      </c>
-      <c r="K80" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="L80" s="49" t="inlineStr">
         <is>
           <t>New</t>
@@ -6117,7 +6093,7 @@
       </c>
       <c r="M80" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the California sales contact. UL-listed lightning-protection materials distributor (UL 96A / NFPA 780 / LPI-175). Adjacent supplier, not a local installer — useful for installer referrals.</t>
+          <t>Owner-direct contact is published for Jeff Owens; confirm they are still the current equity owner. Dedicated residential and commercial surge-protection page, including lightning-caused surges. Family-owned since 1965; CSLB #464389. 279 N Amphlett Blvd.</t>
         </is>
       </c>
       <c r="N80" s="49" t="inlineStr">
@@ -6134,7 +6110,7 @@
     <row r="81" ht="48" customHeight="1" s="47">
       <c r="A81" s="49" t="inlineStr">
         <is>
-          <t>Bonded Lightning Protection (national specialist)</t>
+          <t>Mr. Prime Electrical</t>
         </is>
       </c>
       <c r="B81" s="49" t="inlineStr">
@@ -6144,17 +6120,17 @@
       </c>
       <c r="C81" s="49" t="inlineStr">
         <is>
-          <t>Serves CA projects; HQ Jupiter, FL</t>
+          <t>Burlingame, CA (San Mateo)</t>
         </is>
       </c>
       <c r="D81" s="49" t="inlineStr">
         <is>
-          <t>Dillon family</t>
+          <t>Jeff Balich (acquired from founder Martin Balich)</t>
         </is>
       </c>
       <c r="E81" s="50" t="inlineStr">
         <is>
-          <t>(561) 746-4336</t>
+          <t>(650) 727-3156</t>
         </is>
       </c>
       <c r="F81" s="49" t="inlineStr">
@@ -6163,7 +6139,7 @@
         </is>
       </c>
       <c r="G81" s="49" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H81" s="49" t="inlineStr">
         <is>
@@ -6177,7 +6153,7 @@
       </c>
       <c r="J81" s="49" t="inlineStr">
         <is>
-          <t>https://bondedlightning.com/</t>
+          <t>https://mrprimeelectrical.com/</t>
         </is>
       </c>
       <c r="K81" s="49" t="inlineStr">
@@ -6192,7 +6168,7 @@
       </c>
       <c r="M81" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the current principal. Pure-play lightning-protection contractor (family-owned). Confirm whether they currently bid Bay Area work before a local-owner conversation.</t>
+          <t>Business line: ask for Jeff Balich and confirm current ownership. Homepage advertises whole-home surge protection. License issued 1970; current owner acquired 1995. CSLB C-10 #264901. 511 Burlingame Ave. Distinct from Mr. Electric of San Jose on the prior list.</t>
         </is>
       </c>
       <c r="N81" s="49" t="inlineStr">
@@ -6209,7 +6185,7 @@
     <row r="82" ht="48" customHeight="1" s="47">
       <c r="A82" s="49" t="inlineStr">
         <is>
-          <t>Myers Container Management Services</t>
+          <t>Container Management Services, LLC (Myers Container)</t>
         </is>
       </c>
       <c r="B82" s="49" t="inlineStr">
@@ -6224,29 +6200,29 @@
       </c>
       <c r="D82" s="49" t="inlineStr">
         <is>
+          <t>Kyle Stavig (CEO, Myers Container / Stavig family)</t>
+        </is>
+      </c>
+      <c r="E82" s="50" t="inlineStr">
+        <is>
+          <t>(800) 406-9377</t>
+        </is>
+      </c>
+      <c r="F82" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G82" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E82" s="50" t="inlineStr">
-        <is>
-          <t>(800) 406-9377</t>
-        </is>
-      </c>
-      <c r="F82" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G82" s="49" t="inlineStr">
+      <c r="H82" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="H82" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="I82" s="49" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -6254,12 +6230,12 @@
       </c>
       <c r="J82" s="49" t="inlineStr">
         <is>
-          <t>https://resource.stopwaste.org/vendor/myers-container-management-services-hayward-21301-cloud-way</t>
+          <t>https://myerscontainer.com/</t>
         </is>
       </c>
       <c r="K82" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>jrodriguez@myerscontainer.com</t>
         </is>
       </c>
       <c r="L82" s="49" t="inlineStr">
@@ -6269,7 +6245,7 @@
       </c>
       <c r="M82" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the Hayward plant manager and confirm current ownership. Direct metal/plastic drum and barrel reconditioning and recycling. 21301 Cloud Way, Hayward, CA 94545.</t>
+          <t>Business line: ask for Kyle Stavig or Hayward ops (Joe Gresenz) and confirm current ownership. Strongest local drum fit: EPA inventory lists Myers CMS at 21301 Cloud Way as an open drum reconditioner. Metal/plastic drum and barrel reconditioning and recycling.</t>
         </is>
       </c>
       <c r="N82" s="49" t="inlineStr">
@@ -6286,7 +6262,7 @@
     <row r="83" ht="48" customHeight="1" s="47">
       <c r="A83" s="49" t="inlineStr">
         <is>
-          <t>IBC Tanks Recycling</t>
+          <t>Containers Unlimited (The Cary Company)</t>
         </is>
       </c>
       <c r="B83" s="49" t="inlineStr">
@@ -6296,34 +6272,32 @@
       </c>
       <c r="C83" s="49" t="inlineStr">
         <is>
-          <t>Hayward, CA (Alameda)</t>
+          <t>Livermore, CA (Alameda); historically Hayward/Oakland</t>
         </is>
       </c>
       <c r="D83" s="49" t="inlineStr">
         <is>
+          <t>Mike McGuire (former owner; stayed as regional VP after 2021 Cary sale)</t>
+        </is>
+      </c>
+      <c r="E83" s="50" t="inlineStr">
+        <is>
+          <t>(510) 887-9277</t>
+        </is>
+      </c>
+      <c r="F83" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G83" s="49" t="n">
+        <v>43</v>
+      </c>
+      <c r="H83" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E83" s="50" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="F83" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G83" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="H83" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="I83" s="49" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -6331,12 +6305,12 @@
       </c>
       <c r="J83" s="49" t="inlineStr">
         <is>
-          <t>https://www.ibctanksrecycling.com/</t>
+          <t>https://containersunlimited.com/</t>
         </is>
       </c>
       <c r="K83" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>cu@thecarycompany.com</t>
         </is>
       </c>
       <c r="L83" s="49" t="inlineStr">
@@ -6346,7 +6320,7 @@
       </c>
       <c r="M83" s="49" t="inlineStr">
         <is>
-          <t>Ask for the current owner. Hayward facility buys, sells, steam-cleans, and reconditions IBC totes (FDA-compliant washes). Verify a published phone and legal entity on the call.</t>
+          <t>Business line: ask for Mike McGuire and confirm current local decision rights. Founded 1983; drums, pails, and IBCs. Livermore is the current distribution/regional office; dedicated reconditioning plant is in Jurupa Valley. StopWaste still lists Hayward take-back.</t>
         </is>
       </c>
       <c r="N83" s="49" t="inlineStr">
@@ -6363,7 +6337,7 @@
     <row r="84" ht="48" customHeight="1" s="47">
       <c r="A84" s="49" t="inlineStr">
         <is>
-          <t>Container Technology, Inc. / IBC Recon Services — Hayward</t>
+          <t>National Tank Services (Trimac) — Hayward wash</t>
         </is>
       </c>
       <c r="B84" s="49" t="inlineStr">
@@ -6378,12 +6352,12 @@
       </c>
       <c r="D84" s="49" t="inlineStr">
         <is>
-          <t>J. Jesus Miramontes (Hayward Plant Manager)</t>
+          <t>Not publicly verified (Trimac Transportation trade name)</t>
         </is>
       </c>
       <c r="E84" s="50" t="inlineStr">
         <is>
-          <t>(800) 295-5510</t>
+          <t>(510) 972-9331</t>
         </is>
       </c>
       <c r="F84" s="49" t="inlineStr">
@@ -6408,7 +6382,7 @@
       </c>
       <c r="J84" s="49" t="inlineStr">
         <is>
-          <t>https://www.containertechnology.com/locations</t>
+          <t>https://www.nationaltankservices.com/</t>
         </is>
       </c>
       <c r="K84" s="49" t="inlineStr">
@@ -6423,7 +6397,7 @@
       </c>
       <c r="M84" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for J. Jesus Miramontes and confirm local P&amp;L ownership (corporate HQ Las Vegas). IBC reconditioning/cleaning warehouse in Hayward; also (509) 851-3117 quote line.</t>
+          <t>Business line: ask for the Hayward washrack manager. Confirmed tank-trailer wash at 3751 Breakwater Ave. Washrack also (510) 293-6838. Distinct from Quala/HTI/DCI. Hayward menu is chemical/latex tank-trailer wash; tote/IBC is a company-wide offering at other shops.</t>
         </is>
       </c>
       <c r="N84" s="49" t="inlineStr">
@@ -6440,7 +6414,7 @@
     <row r="85" ht="48" customHeight="1" s="47">
       <c r="A85" s="49" t="inlineStr">
         <is>
-          <t>Kleen Industrial Services, Inc.</t>
+          <t>ACTenviro (Advanced Chemical Transport)</t>
         </is>
       </c>
       <c r="B85" s="49" t="inlineStr">
@@ -6450,34 +6424,32 @@
       </c>
       <c r="C85" s="49" t="inlineStr">
         <is>
-          <t>Danville, CA (Contra Costa)</t>
+          <t>San Jose, CA (Santa Clara)</t>
         </is>
       </c>
       <c r="D85" s="49" t="inlineStr">
         <is>
+          <t>Not publicly verified (Republic Services parent; Tim Smith listed as CEO)</t>
+        </is>
+      </c>
+      <c r="E85" s="50" t="inlineStr">
+        <is>
+          <t>(408) 548-5050</t>
+        </is>
+      </c>
+      <c r="F85" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G85" s="49" t="n">
+        <v>26</v>
+      </c>
+      <c r="H85" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E85" s="50" t="inlineStr">
-        <is>
-          <t>(925) 831-9802</t>
-        </is>
-      </c>
-      <c r="F85" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G85" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="H85" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="I85" s="49" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -6485,12 +6457,12 @@
       </c>
       <c r="J85" s="49" t="inlineStr">
         <is>
-          <t>https://www.kleenindustrialservices.com/</t>
+          <t>https://www.actenviro.com/</t>
         </is>
       </c>
       <c r="K85" s="49" t="inlineStr">
         <is>
-          <t>info@kleenindustrialservices.com</t>
+          <t>info@actenviro.com</t>
         </is>
       </c>
       <c r="L85" s="49" t="inlineStr">
@@ -6500,7 +6472,7 @@
       </c>
       <c r="M85" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the current owner. Hazardous/non-hazardous drum removal, vacuum-truck, and industrial-waste services. 50 Oak Court, Danville. Also (800) 356-7323 / (925) 831-9183.</t>
+          <t>Business line: ask for the San Jose branch manager. Founded 2000. 967 Mabury Rd. Storage-tank steam-cleaning, UST cleaning, portable-tank cleaning, and vacuum-truck work. Adjacent industrial tank cleaning, not a drum-reconditioning plant. Emergency (866) 348-2800.</t>
         </is>
       </c>
       <c r="N85" s="49" t="inlineStr">
@@ -6517,7 +6489,7 @@
     <row r="86" ht="48" customHeight="1" s="47">
       <c r="A86" s="49" t="inlineStr">
         <is>
-          <t>Heritage-Crystal Clean — Hayward / Oakland branch</t>
+          <t>Patriot Environmental Services — Richmond</t>
         </is>
       </c>
       <c r="B86" s="49" t="inlineStr">
@@ -6527,17 +6499,17 @@
       </c>
       <c r="C86" s="49" t="inlineStr">
         <is>
-          <t>Hayward, CA (Alameda)</t>
+          <t>Richmond, CA (Contra Costa)</t>
         </is>
       </c>
       <c r="D86" s="49" t="inlineStr">
         <is>
-          <t>Corporate branch; local owner not applicable</t>
+          <t>Kent Bartley (CEO) / Josh Teves (President); Tom Salazar (Richmond Operations Manager)</t>
         </is>
       </c>
       <c r="E86" s="50" t="inlineStr">
         <is>
-          <t>(877) 938-7948</t>
+          <t>(800) 624-9136</t>
         </is>
       </c>
       <c r="F86" s="49" t="inlineStr">
@@ -6545,8 +6517,10 @@
           <t>Business Line</t>
         </is>
       </c>
-      <c r="G86" s="49" t="n">
-        <v>27</v>
+      <c r="G86" s="49" t="inlineStr">
+        <is>
+          <t>Not publicly verified</t>
+        </is>
       </c>
       <c r="H86" s="49" t="inlineStr">
         <is>
@@ -6560,12 +6534,12 @@
       </c>
       <c r="J86" s="49" t="inlineStr">
         <is>
-          <t>https://www.crystal-clean.com/stores/environmental-services-branch-oakland-california/</t>
+          <t>https://www.patriotenvironmental.com/locations/</t>
         </is>
       </c>
       <c r="K86" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>contact@patriotenv.com</t>
         </is>
       </c>
       <c r="L86" s="49" t="inlineStr">
@@ -6575,7 +6549,7 @@
       </c>
       <c r="M86" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the Hayward branch manager. Waste-drum disposal, parts cleaners, and used-oil services. 23271 Eichler St, Bldg 10. National platform — confirm local decision rights.</t>
+          <t>Business line: ask for Tom Salazar and confirm local decision rights (Heritage-Crystal Clean subsidiary since 2022). Hydroblasting, tank/vessel cleaning, vacuum work. 255 Parr Blvd. 24-hr dispatch (855) 666-4299.</t>
         </is>
       </c>
       <c r="N86" s="49" t="inlineStr">
@@ -6592,7 +6566,7 @@
     <row r="87" ht="48" customHeight="1" s="47">
       <c r="A87" s="49" t="inlineStr">
         <is>
-          <t>CAL INC</t>
+          <t>Clean Harbors — Benicia Industrial Services</t>
         </is>
       </c>
       <c r="B87" s="49" t="inlineStr">
@@ -6602,49 +6576,47 @@
       </c>
       <c r="C87" s="49" t="inlineStr">
         <is>
-          <t>Vacaville, CA (Solano)</t>
+          <t>Benicia, CA (Solano)</t>
         </is>
       </c>
       <c r="D87" s="49" t="inlineStr">
         <is>
+          <t>Alan S. McKim (Chairman/CTO; public company)</t>
+        </is>
+      </c>
+      <c r="E87" s="50" t="inlineStr">
+        <is>
+          <t>(707) 747-6699</t>
+        </is>
+      </c>
+      <c r="F87" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G87" s="49" t="n">
+        <v>46</v>
+      </c>
+      <c r="H87" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E87" s="50" t="inlineStr">
-        <is>
-          <t>(800) 359-4467</t>
-        </is>
-      </c>
-      <c r="F87" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G87" s="49" t="inlineStr">
+      <c r="I87" s="49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J87" s="49" t="inlineStr">
+        <is>
+          <t>https://www.cleanharbors.com/location/benicia-industrial-services</t>
+        </is>
+      </c>
+      <c r="K87" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="H87" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="I87" s="49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J87" s="49" t="inlineStr">
-        <is>
-          <t>https://cal-inc.com/abatement/industrialcleaning.php</t>
-        </is>
-      </c>
-      <c r="K87" s="49" t="inlineStr">
-        <is>
-          <t>tesparza@cal-inc.com</t>
-        </is>
-      </c>
       <c r="L87" s="49" t="inlineStr">
         <is>
           <t>New</t>
@@ -6652,7 +6624,7 @@
       </c>
       <c r="M87" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for estimating (T. Esparza) and the current owner. Industrial tank, vessel, vacuum-truck, and hydroblast cleaning across the Bay Area and Northern California.</t>
+          <t>Business line: ask for the Benicia yard manager. 4101 Industrial Way. Corporate industrial services include tank/vessel cleaning, vacuum, hydroblast/steam, and ISO/rail-car container cleaning. Confirm local wash-rack scope on the call.</t>
         </is>
       </c>
       <c r="N87" s="49" t="inlineStr">
@@ -6669,7 +6641,7 @@
     <row r="88" ht="48" customHeight="1" s="47">
       <c r="A88" s="49" t="inlineStr">
         <is>
-          <t>ADCO Services</t>
+          <t>CAL INC</t>
         </is>
       </c>
       <c r="B88" s="49" t="inlineStr">
@@ -6679,17 +6651,17 @@
       </c>
       <c r="C88" s="49" t="inlineStr">
         <is>
-          <t>Serves Antioch / Martinez / Vacaville, CA</t>
+          <t>Vacaville, CA (Solano)</t>
         </is>
       </c>
       <c r="D88" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>David Esparza (President/CEO); Sandy Esparza (co-founder/VP)</t>
         </is>
       </c>
       <c r="E88" s="50" t="inlineStr">
         <is>
-          <t>(877) 254-2326</t>
+          <t>(707) 446-7996</t>
         </is>
       </c>
       <c r="F88" s="49" t="inlineStr">
@@ -6697,15 +6669,11 @@
           <t>Business Line</t>
         </is>
       </c>
-      <c r="G88" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="H88" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
+      <c r="G88" s="49" t="n">
+        <v>47</v>
+      </c>
+      <c r="H88" s="49" t="n">
+        <v>70</v>
       </c>
       <c r="I88" s="49" t="inlineStr">
         <is>
@@ -6714,12 +6682,12 @@
       </c>
       <c r="J88" s="49" t="inlineStr">
         <is>
-          <t>https://www.americanwastehaulers.com/hazardous-waste-disposal-california</t>
+          <t>https://cal-inc.com/</t>
         </is>
       </c>
       <c r="K88" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>desparza@cal-inc.com</t>
         </is>
       </c>
       <c r="L88" s="49" t="inlineStr">
@@ -6729,7 +6697,7 @@
       </c>
       <c r="M88" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the California operations contact. Advertises tank clean-outs and hazardous-waste disposal in East Bay/Solano cities. Confirm a Bay Area operating base versus out-of-area dispatch.</t>
+          <t>Business line: ask for David Esparza and confirm current ownership. Founded 1979. On-site tank, vessel, separator, hydroblast, and vacuum-truck cleaning across the Bay Area. Toll-free (800) 359-4467. Estimating: tesparza@cal-inc.com.</t>
         </is>
       </c>
       <c r="N88" s="49" t="inlineStr">
@@ -6746,7 +6714,7 @@
     <row r="89" ht="48" customHeight="1" s="47">
       <c r="A89" s="49" t="inlineStr">
         <is>
-          <t>Patriot Environmental Services — Richmond</t>
+          <t>Triumvirate Environmental — San Leandro</t>
         </is>
       </c>
       <c r="B89" s="49" t="inlineStr">
@@ -6756,17 +6724,17 @@
       </c>
       <c r="C89" s="49" t="inlineStr">
         <is>
-          <t>Richmond, CA (Contra Costa)</t>
+          <t>San Leandro, CA (Alameda)</t>
         </is>
       </c>
       <c r="D89" s="49" t="inlineStr">
         <is>
-          <t>Tom Salazar (Operations Manager)</t>
+          <t>John F. McQuillan (Founder/CEO/Chairman)</t>
         </is>
       </c>
       <c r="E89" s="50" t="inlineStr">
         <is>
-          <t>(800) 624-9136</t>
+          <t>(510) 447-5688</t>
         </is>
       </c>
       <c r="F89" s="49" t="inlineStr">
@@ -6774,31 +6742,29 @@
           <t>Business Line</t>
         </is>
       </c>
-      <c r="G89" s="49" t="inlineStr">
+      <c r="G89" s="49" t="n">
+        <v>38</v>
+      </c>
+      <c r="H89" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="H89" s="49" t="inlineStr">
+      <c r="I89" s="49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J89" s="49" t="inlineStr">
+        <is>
+          <t>https://www.triumvirate.com/locations/pacific/san-leandro-ca</t>
+        </is>
+      </c>
+      <c r="K89" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="I89" s="49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J89" s="49" t="inlineStr">
-        <is>
-          <t>https://www.patriotenvironmental.com/locations/</t>
-        </is>
-      </c>
-      <c r="K89" s="49" t="inlineStr">
-        <is>
-          <t>contact@patriotenv.com</t>
-        </is>
-      </c>
       <c r="L89" s="49" t="inlineStr">
         <is>
           <t>New</t>
@@ -6806,7 +6772,7 @@
       </c>
       <c r="M89" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for Tom Salazar and confirm local decision rights (now part of Crystal Clean). Industrial cleaning, tank/field services, and waste management. 255 Parr Blvd, Richmond, CA 94801.</t>
+          <t>Business line: ask for the San Leandro manager. 1599 Factor Ave. Location page states the facility cleans tanks; corporate pages list chemical/process tank cleaning, vacuum trucks, and confined space. Life-sciences/industrial fit, not drum reconditioning. Sales (888) 834-9697.</t>
         </is>
       </c>
       <c r="N89" s="49" t="inlineStr">
@@ -6823,7 +6789,7 @@
     <row r="90" ht="48" customHeight="1" s="47">
       <c r="A90" s="49" t="inlineStr">
         <is>
-          <t>Bayarea Terminals (ISO tank depot brand)</t>
+          <t>Golden Gate Tank Removal, Inc.</t>
         </is>
       </c>
       <c r="B90" s="49" t="inlineStr">
@@ -6833,49 +6799,45 @@
       </c>
       <c r="C90" s="49" t="inlineStr">
         <is>
-          <t>Oakland-branded ISO tank services (verify CA depot)</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D90" s="49" t="inlineStr">
         <is>
+          <t>Tim Hallen (President; BBB). CA SOS has also listed Gina Abo Wee as CEO/CFO</t>
+        </is>
+      </c>
+      <c r="E90" s="50" t="inlineStr">
+        <is>
+          <t>(415) 512-1555</t>
+        </is>
+      </c>
+      <c r="F90" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G90" s="49" t="n">
+        <v>31</v>
+      </c>
+      <c r="H90" s="49" t="n">
+        <v>15</v>
+      </c>
+      <c r="I90" s="49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J90" s="49" t="inlineStr">
+        <is>
+          <t>https://ggtr.com/</t>
+        </is>
+      </c>
+      <c r="K90" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E90" s="50" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="F90" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G90" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="H90" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="I90" s="49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J90" s="49" t="inlineStr">
-        <is>
-          <t>https://bayareapl.com/tank-container-service/</t>
-        </is>
-      </c>
-      <c r="K90" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="L90" s="49" t="inlineStr">
         <is>
           <t>New</t>
@@ -6883,7 +6845,7 @@
       </c>
       <c r="M90" s="49" t="inlineStr">
         <is>
-          <t>Ask for the depot manager. Site describes Groninger automated ISO-tank and road-tanker cleaning. Corporate pages also reference India facilities — verify a live Oakland/Bay Area depot before outreach.</t>
+          <t>Business line: ask for Tim Hallen and confirm current ownership. UST cleaning, removal, and closure since 1995. CSLB #616521 (A/HAZ). 1480 Carroll Ave. Adjacent industrial tank cleaning, not drum/IBC depot work.</t>
         </is>
       </c>
       <c r="N90" s="49" t="inlineStr">
@@ -6900,7 +6862,7 @@
     <row r="91" ht="48" customHeight="1" s="47">
       <c r="A91" s="49" t="inlineStr">
         <is>
-          <t>Hoover CS — IBC / tote / ISO tank cleaning</t>
+          <t>Questar Inc. / Questar Solutions — Hayward</t>
         </is>
       </c>
       <c r="B91" s="49" t="inlineStr">
@@ -6910,49 +6872,47 @@
       </c>
       <c r="C91" s="49" t="inlineStr">
         <is>
-          <t>Serves West Coast; confirm Bay Area depot</t>
+          <t>Hayward, CA (Alameda)</t>
         </is>
       </c>
       <c r="D91" s="49" t="inlineStr">
         <is>
+          <t>Not publicly verified (Doug Rountree listed as manager on a third-party directory)</t>
+        </is>
+      </c>
+      <c r="E91" s="50" t="inlineStr">
+        <is>
+          <t>(510) 324-1333</t>
+        </is>
+      </c>
+      <c r="F91" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G91" s="49" t="n">
+        <v>36</v>
+      </c>
+      <c r="H91" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E91" s="50" t="inlineStr">
+      <c r="I91" s="49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J91" s="49" t="inlineStr">
+        <is>
+          <t>https://www.questarsolutions.com/</t>
+        </is>
+      </c>
+      <c r="K91" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="F91" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G91" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="H91" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="I91" s="49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J91" s="49" t="inlineStr">
-        <is>
-          <t>https://hooversolutions.com/services/tank-cleaning-and-maintenance/</t>
-        </is>
-      </c>
-      <c r="K91" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="L91" s="49" t="inlineStr">
         <is>
           <t>New</t>
@@ -6960,7 +6920,7 @@
       </c>
       <c r="M91" s="49" t="inlineStr">
         <is>
-          <t>Ask for the Western/California depot contact. Certified IBC, tote, and ISO tank wash/retest. Confirm a Bay Area operating location; do not treat as a local owner-operator until verified.</t>
+          <t>Business line: ask for the Hayward yard manager. 30983 San Clemente St. StopWaste documents metal/plastic/fiber drum take-back; Questar sells new and reconditioned drums and IBC totes. Reconditioned-drum supply/take-back, not a confirmed on-site industrial wash line.</t>
         </is>
       </c>
       <c r="N91" s="49" t="inlineStr">

--- a/Builder + Caller Masterlist - SBC 2026.xlsx
+++ b/Builder + Caller Masterlist - SBC 2026.xlsx
@@ -1511,7 +1511,7 @@
       </c>
       <c r="C20" s="49" t="inlineStr">
         <is>
-          <t>San Jose, CA (Santa Clara)</t>
+          <t>Santa Clara, CA (Santa Clara)</t>
         </is>
       </c>
       <c r="D20" s="49" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="K20" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>tbm@tbmfirst.net</t>
         </is>
       </c>
       <c r="L20" s="49" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="M20" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the current owner or president. Commercial janitorial since 1986; green cleaning, window, carpet, pressure washing, and cleanroom work across Silicon Valley.</t>
+          <t>Business line: ask for the current owner or president. Commercial janitorial since 1986 at 3020 Scott Blvd; green cleaning, window, carpet, pressure washing, and cleanroom work.</t>
         </is>
       </c>
       <c r="N20" s="49" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="C23" s="49" t="inlineStr">
         <is>
-          <t>Walnut Creek / East Bay, CA</t>
+          <t>Walnut Creek, CA (Contra Costa)</t>
         </is>
       </c>
       <c r="D23" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>Matthew C. Townsend</t>
         </is>
       </c>
       <c r="E23" s="50" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="K23" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>info@tsmaintenance.com</t>
         </is>
       </c>
       <c r="L23" s="49" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="M23" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the current owner. 25+ years of industrial, corporate, and small-business janitorial; green-cleaning programs.</t>
+          <t>Business line: ask for Matthew C. Townsend and confirm current ownership. 25+ years of industrial, corporate, and small-business janitorial. 1601 N California Blvd, Ste 250. Distinct from Tetra Maintenance.</t>
         </is>
       </c>
       <c r="N23" s="49" t="inlineStr">
@@ -1979,16 +1979,14 @@
           <t>Business Line</t>
         </is>
       </c>
-      <c r="G26" s="49" t="inlineStr">
+      <c r="G26" s="49" t="n">
+        <v>50</v>
+      </c>
+      <c r="H26" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="H26" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="I26" s="49" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2001,7 +1999,7 @@
       </c>
       <c r="K26" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>info@grapevinejanitorial.com</t>
         </is>
       </c>
       <c r="L26" s="49" t="inlineStr">
@@ -2011,7 +2009,7 @@
       </c>
       <c r="M26" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the current owner. Commercial/industrial janitorial for offices, manufacturing, warehouses, and retail in Napa Valley. PO Box 3124.</t>
+          <t>Business line: ask for the current owner. Wine Country commercial/industrial janitorial since 1976. PO Box 3124, Napa.</t>
         </is>
       </c>
       <c r="N26" s="49" t="inlineStr">
@@ -2255,7 +2253,7 @@
     <row r="30" ht="48" customHeight="1" s="47">
       <c r="A30" s="49" t="inlineStr">
         <is>
-          <t>North Bay Building Maintenance Company</t>
+          <t>SourceONE Building Maintenance, Inc.</t>
         </is>
       </c>
       <c r="B30" s="49" t="inlineStr">
@@ -2265,7 +2263,7 @@
       </c>
       <c r="C30" s="49" t="inlineStr">
         <is>
-          <t>San Jose, CA (Santa Clara)</t>
+          <t>Santa Clara, CA (Santa Clara)</t>
         </is>
       </c>
       <c r="D30" s="49" t="inlineStr">
@@ -2275,7 +2273,7 @@
       </c>
       <c r="E30" s="50" t="inlineStr">
         <is>
-          <t>(408) 528-4238</t>
+          <t>(408) 437-3046</t>
         </is>
       </c>
       <c r="F30" s="49" t="inlineStr">
@@ -2284,7 +2282,7 @@
         </is>
       </c>
       <c r="G30" s="49" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H30" s="49" t="inlineStr">
         <is>
@@ -2293,17 +2291,17 @@
       </c>
       <c r="I30" s="49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J30" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>https://www.sourceonebuildingmtn.com/</t>
         </is>
       </c>
       <c r="K30" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>jnigro@source1services.net</t>
         </is>
       </c>
       <c r="L30" s="49" t="inlineStr">
@@ -2313,7 +2311,7 @@
       </c>
       <c r="M30" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the current owner. Blue Book: in business since 1999; complete janitorial and exterior building cleaning across the nine-county Bay Area.</t>
+          <t>Business line: ask for the current owner. Veteran-owned commercial janitorial for offices, labs, cleanrooms, and GMP/biotech. 2974 Scott Blvd. Public listings cite ISO 9001:2015.</t>
         </is>
       </c>
       <c r="N30" s="49" t="inlineStr">
@@ -2330,7 +2328,7 @@
     <row r="31" ht="48" customHeight="1" s="47">
       <c r="A31" s="49" t="inlineStr">
         <is>
-          <t>Maintenance Systems Management, Inc.</t>
+          <t>Altos Building Maintenance</t>
         </is>
       </c>
       <c r="B31" s="49" t="inlineStr">
@@ -2340,32 +2338,32 @@
       </c>
       <c r="C31" s="49" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Santa Clara, CA (Santa Clara)</t>
         </is>
       </c>
       <c r="D31" s="49" t="inlineStr">
         <is>
+          <t>Roger Cruickshank (Founder)</t>
+        </is>
+      </c>
+      <c r="E31" s="50" t="inlineStr">
+        <is>
+          <t>(408) 480-1630</t>
+        </is>
+      </c>
+      <c r="F31" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G31" s="49" t="n">
+        <v>38</v>
+      </c>
+      <c r="H31" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E31" s="50" t="inlineStr">
-        <is>
-          <t>(415) 920-3840</t>
-        </is>
-      </c>
-      <c r="F31" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G31" s="49" t="n">
-        <v>37</v>
-      </c>
-      <c r="H31" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="I31" s="49" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2373,12 +2371,12 @@
       </c>
       <c r="J31" s="49" t="inlineStr">
         <is>
-          <t>https://msm-inc.com/</t>
+          <t>https://altosmaint.com/</t>
         </is>
       </c>
       <c r="K31" s="49" t="inlineStr">
         <is>
-          <t>sales@msm-inc.com</t>
+          <t>chase@altosmaint.com</t>
         </is>
       </c>
       <c r="L31" s="49" t="inlineStr">
@@ -2388,7 +2386,7 @@
       </c>
       <c r="M31" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the president/owner (site says owner-operated since 1989). Contract custodial for offices, schools, retail, and property managers. 2415 Third St, Ste 257.</t>
+          <t>Business line: ask for Roger Cruickshank and confirm current ownership. Founded 1988. 3080 Olcott St, Ste 105B. Serves Santa Clara, San Jose, Mountain View, and Sunnyvale.</t>
         </is>
       </c>
       <c r="N31" s="49" t="inlineStr">
@@ -2881,16 +2879,14 @@
           <t>Business Line</t>
         </is>
       </c>
-      <c r="G38" s="49" t="inlineStr">
+      <c r="G38" s="49" t="n">
+        <v>21</v>
+      </c>
+      <c r="H38" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="H38" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="I38" s="49" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2898,12 +2894,12 @@
       </c>
       <c r="J38" s="49" t="inlineStr">
         <is>
-          <t>http://www.pcsmaint.com/</t>
+          <t>https://pcsmaint.com/</t>
         </is>
       </c>
       <c r="K38" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>pcs-operations@att.net</t>
         </is>
       </c>
       <c r="L38" s="49" t="inlineStr">
@@ -2913,7 +2909,7 @@
       </c>
       <c r="M38" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the current owner. IJCSA-certified commercial/residential cleaning; 280 Newhall St, San Francisco. Also lists an LA address on the same phone.</t>
+          <t>Business line: ask for the current owner. IJCSA/BSCAI-listed commercial/residential cleaning; founded 2005. 280 Newhall St. Distinct from Professional Cleaning Systems on the prior list.</t>
         </is>
       </c>
       <c r="N38" s="49" t="inlineStr">
@@ -3335,31 +3331,29 @@
           <t>Business Line</t>
         </is>
       </c>
-      <c r="G44" s="49" t="inlineStr">
+      <c r="G44" s="49" t="n">
+        <v>24</v>
+      </c>
+      <c r="H44" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="H44" s="49" t="inlineStr">
+      <c r="I44" s="49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J44" s="49" t="inlineStr">
+        <is>
+          <t>https://eveningjanitorial.com/</t>
+        </is>
+      </c>
+      <c r="K44" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="I44" s="49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J44" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="K44" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="L44" s="49" t="inlineStr">
         <is>
           <t>New</t>
@@ -3367,7 +3361,7 @@
       </c>
       <c r="M44" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the current owner. Public listings describe office and manufacturing janitorial from Walnut Creek across the East Bay. Verify website and ownership on the call.</t>
+          <t>Business line: ask for the current owner. Family-run East Bay commercial cleaning for offices, schools, and light industrial since 2002. 10 Jolie Ln. Some directories also list (925) 437-9001.</t>
         </is>
       </c>
       <c r="N44" s="49" t="inlineStr">
@@ -3384,7 +3378,7 @@
     <row r="45" ht="48" customHeight="1" s="47">
       <c r="A45" s="49" t="inlineStr">
         <is>
-          <t>ServiceMaster Janitorial by Pratik</t>
+          <t>A &amp; K Janitorial Inc.</t>
         </is>
       </c>
       <c r="B45" s="49" t="inlineStr">
@@ -3394,45 +3388,45 @@
       </c>
       <c r="C45" s="49" t="inlineStr">
         <is>
-          <t>Hayward, CA (Alameda)</t>
+          <t>San Jose, CA (Santa Clara)</t>
         </is>
       </c>
       <c r="D45" s="49" t="inlineStr">
         <is>
-          <t>Pratik (public principal; surname not displayed)</t>
+          <t>Not publicly verified</t>
         </is>
       </c>
       <c r="E45" s="50" t="inlineStr">
         <is>
+          <t>(408) 532-6889</t>
+        </is>
+      </c>
+      <c r="F45" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G45" s="49" t="n">
+        <v>33</v>
+      </c>
+      <c r="H45" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="F45" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G45" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="H45" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="I45" s="49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J45" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>https://www.aandkjanitorial.com/</t>
         </is>
       </c>
       <c r="K45" s="49" t="inlineStr">
         <is>
-          <t>info@smjbypratik.com</t>
+          <t>jramirez@aandkjanitorial.com</t>
         </is>
       </c>
       <c r="L45" s="49" t="inlineStr">
@@ -3442,7 +3436,7 @@
       </c>
       <c r="M45" s="49" t="inlineStr">
         <is>
-          <t>Ask for Pratik and confirm current ownership. LinkedIn: Hayward HQ, 1–10 employees; disinfection and janitorial. Verify working phone during the call.</t>
+          <t>Business line: ask for the current owner. Family-owned commercial janitorial since 1993 for medical offices, schools, corporate, dealerships, and hotels.</t>
         </is>
       </c>
       <c r="N45" s="49" t="inlineStr">
@@ -3459,7 +3453,7 @@
     <row r="46" ht="48" customHeight="1" s="47">
       <c r="A46" s="49" t="inlineStr">
         <is>
-          <t>Performance First Building Services, Inc.</t>
+          <t>JP Enterprises Janitorial</t>
         </is>
       </c>
       <c r="B46" s="49" t="inlineStr">
@@ -3469,47 +3463,45 @@
       </c>
       <c r="C46" s="49" t="inlineStr">
         <is>
-          <t>Santa Clara, CA (Santa Clara)</t>
+          <t>San Mateo, CA (San Mateo)</t>
         </is>
       </c>
       <c r="D46" s="49" t="inlineStr">
         <is>
+          <t>John Velichko and Peter Velichko (Founders)</t>
+        </is>
+      </c>
+      <c r="E46" s="50" t="inlineStr">
+        <is>
+          <t>(650) 348-8991</t>
+        </is>
+      </c>
+      <c r="F46" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G46" s="49" t="n">
+        <v>40</v>
+      </c>
+      <c r="H46" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E46" s="50" t="inlineStr">
-        <is>
-          <t>(408) 441-4632</t>
-        </is>
-      </c>
-      <c r="F46" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G46" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="H46" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="I46" s="49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J46" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>https://sanmateobestjanitorial.com/</t>
         </is>
       </c>
       <c r="K46" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>jpentrp@aol.com</t>
         </is>
       </c>
       <c r="L46" s="49" t="inlineStr">
@@ -3519,7 +3511,7 @@
       </c>
       <c r="M46" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the current owner. Public directories list a Santa Clara commercial building-services firm. Website (perfirst.com) was not live at compile time; verify fit on the call.</t>
+          <t>Business line: ask for John or Peter Velichko and confirm current ownership. Peninsula janitorial since 1986. 3315 Marisma St.</t>
         </is>
       </c>
       <c r="N46" s="49" t="inlineStr">
@@ -3536,7 +3528,7 @@
     <row r="47" ht="48" customHeight="1" s="47">
       <c r="A47" s="49" t="inlineStr">
         <is>
-          <t>Apex Business Services, Inc. (Apex Construction Janitorial)</t>
+          <t>All Janitorial Service, Inc.</t>
         </is>
       </c>
       <c r="B47" s="49" t="inlineStr">
@@ -3546,47 +3538,47 @@
       </c>
       <c r="C47" s="49" t="inlineStr">
         <is>
-          <t>San Jose, CA (Santa Clara)</t>
+          <t>Redwood City, CA (San Mateo)</t>
         </is>
       </c>
       <c r="D47" s="49" t="inlineStr">
         <is>
+          <t>Christian (Chris) Ramirez (CEO)</t>
+        </is>
+      </c>
+      <c r="E47" s="50" t="inlineStr">
+        <is>
+          <t>(650) 261-0723</t>
+        </is>
+      </c>
+      <c r="F47" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G47" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E47" s="50" t="inlineStr">
+      <c r="H47" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="I47" s="49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J47" s="49" t="inlineStr">
+        <is>
+          <t>https://www.alljanitorialservice.com/</t>
+        </is>
+      </c>
+      <c r="K47" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="F47" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G47" s="49" t="n">
-        <v>41</v>
-      </c>
-      <c r="H47" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="I47" s="49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J47" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="K47" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="L47" s="49" t="inlineStr">
         <is>
           <t>New</t>
@@ -3594,7 +3586,7 @@
       </c>
       <c r="M47" s="49" t="inlineStr">
         <is>
-          <t>Ask for the current owner. Blue Book: established 1985; construction/finish janitorial and building maintenance in the South Bay. Verify working phone during the call.</t>
+          <t>Business line: ask for Chris Ramirez and confirm current ownership. In-house commercial janitorial, porter, floor, window, and pressure washing for San Mateo and west Santa Clara. 3130 Spring St.</t>
         </is>
       </c>
       <c r="N47" s="49" t="inlineStr">
@@ -3621,49 +3613,45 @@
       </c>
       <c r="C48" s="49" t="inlineStr">
         <is>
-          <t>Bay Area, CA</t>
+          <t>Santa Rosa, CA (Sonoma)</t>
         </is>
       </c>
       <c r="D48" s="49" t="inlineStr">
         <is>
-          <t>Adolfo Mendoza (CEO)</t>
+          <t>Adolfo Mendoza (President)</t>
         </is>
       </c>
       <c r="E48" s="50" t="inlineStr">
         <is>
+          <t>(707) 586-6640</t>
+        </is>
+      </c>
+      <c r="F48" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G48" s="49" t="n">
+        <v>47</v>
+      </c>
+      <c r="H48" s="49" t="n">
+        <v>45</v>
+      </c>
+      <c r="I48" s="49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J48" s="49" t="inlineStr">
+        <is>
+          <t>https://optimabuildingservices.com/</t>
+        </is>
+      </c>
+      <c r="K48" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="F48" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G48" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="H48" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="I48" s="49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J48" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="K48" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="L48" s="49" t="inlineStr">
         <is>
           <t>New</t>
@@ -3671,7 +3659,7 @@
       </c>
       <c r="M48" s="49" t="inlineStr">
         <is>
-          <t>Ask for Adolfo Mendoza and confirm current ownership. Public profiles describe a Bay Area commercial janitorial/facilities firm. Verify phone, city, and headcount on the call.</t>
+          <t>Business line: ask for Adolfo Mendoza and confirm current ownership. Commercial janitorial, carpet, pressure washing, and construction cleanup since 1979. BBB-accredited; about 45 employees.</t>
         </is>
       </c>
       <c r="N48" s="49" t="inlineStr">
@@ -3688,7 +3676,7 @@
     <row r="49" ht="48" customHeight="1" s="47">
       <c r="A49" s="49" t="inlineStr">
         <is>
-          <t>Redwood Building Maintenance</t>
+          <t>Redwood Building Maintenance, Inc.</t>
         </is>
       </c>
       <c r="B49" s="49" t="inlineStr">
@@ -3698,7 +3686,7 @@
       </c>
       <c r="C49" s="49" t="inlineStr">
         <is>
-          <t>East Bay / Tri-Valley, CA</t>
+          <t>Santa Rosa, CA (Sonoma); South/East Bay ops</t>
         </is>
       </c>
       <c r="D49" s="49" t="inlineStr">
@@ -3708,7 +3696,7 @@
       </c>
       <c r="E49" s="50" t="inlineStr">
         <is>
-          <t>(925) 867-3850</t>
+          <t>(888) 789-0600</t>
         </is>
       </c>
       <c r="F49" s="49" t="inlineStr">
@@ -3716,31 +3704,29 @@
           <t>Business Line</t>
         </is>
       </c>
-      <c r="G49" s="49" t="inlineStr">
+      <c r="G49" s="49" t="n">
+        <v>61</v>
+      </c>
+      <c r="H49" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="H49" s="49" t="inlineStr">
+      <c r="I49" s="49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J49" s="49" t="inlineStr">
+        <is>
+          <t>https://rbmco.com/</t>
+        </is>
+      </c>
+      <c r="K49" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="I49" s="49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J49" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="K49" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="L49" s="49" t="inlineStr">
         <is>
           <t>New</t>
@@ -3748,7 +3734,7 @@
       </c>
       <c r="M49" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the current owner. Public listings place a commercial janitorial provider serving East and South Bay. Confirm legal name, city, and website on the call.</t>
+          <t>Business line: ask for the current owner. Full-service commercial janitorial since 1965. North Bay (888) 789-0600; South &amp; East Bay (925) 867-3850.</t>
         </is>
       </c>
       <c r="N49" s="49" t="inlineStr">
@@ -3765,7 +3751,7 @@
     <row r="50" ht="48" customHeight="1" s="47">
       <c r="A50" s="49" t="inlineStr">
         <is>
-          <t>Commercial Building Maintenance LLC</t>
+          <t>DSP Janitorial Service</t>
         </is>
       </c>
       <c r="B50" s="49" t="inlineStr">
@@ -3775,17 +3761,17 @@
       </c>
       <c r="C50" s="49" t="inlineStr">
         <is>
-          <t>Santa Clara, CA (Santa Clara)</t>
+          <t>Hayward, CA (Alameda)</t>
         </is>
       </c>
       <c r="D50" s="49" t="inlineStr">
         <is>
-          <t>Allen (Owner; given name not fully displayed)</t>
+          <t>Don (first name published; surname not independently verified)</t>
         </is>
       </c>
       <c r="E50" s="50" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>(510) 782-2200</t>
         </is>
       </c>
       <c r="F50" s="49" t="inlineStr">
@@ -3794,26 +3780,24 @@
         </is>
       </c>
       <c r="G50" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="H50" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
+        <v>57</v>
+      </c>
+      <c r="H50" s="49" t="n">
+        <v>20</v>
       </c>
       <c r="I50" s="49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J50" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>https://dspjanitorial.com/</t>
         </is>
       </c>
       <c r="K50" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>don@dspjanitorial.com</t>
         </is>
       </c>
       <c r="L50" s="49" t="inlineStr">
@@ -3823,7 +3807,7 @@
       </c>
       <c r="M50" s="49" t="inlineStr">
         <is>
-          <t>Ask for the owner (BBB lists Allen) and confirm current ownership. BBB: 2445 Augustine Dr #150; founded 2021. Screening concern: public evidence indicates only 5 years in business.</t>
+          <t>Business line: ask for Don and confirm current ownership. Commercial janitorial since 1969. 23762 Foley St #3. About 20 employees per BBB. Serves SF, Alameda, Santa Clara, San Mateo, and Contra Costa.</t>
         </is>
       </c>
       <c r="N50" s="49" t="inlineStr">
@@ -3840,7 +3824,7 @@
     <row r="51" ht="48" customHeight="1" s="47">
       <c r="A51" s="49" t="inlineStr">
         <is>
-          <t>Herreras Cleaning</t>
+          <t>Comet Property Services</t>
         </is>
       </c>
       <c r="B51" s="49" t="inlineStr">
@@ -3850,49 +3834,45 @@
       </c>
       <c r="C51" s="49" t="inlineStr">
         <is>
-          <t>Bay Area, CA</t>
+          <t>Novato, CA (Marin)</t>
         </is>
       </c>
       <c r="D51" s="49" t="inlineStr">
         <is>
+          <t>Richard Basile (Owner)</t>
+        </is>
+      </c>
+      <c r="E51" s="50" t="inlineStr">
+        <is>
+          <t>(415) 382-1150</t>
+        </is>
+      </c>
+      <c r="F51" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G51" s="49" t="n">
+        <v>43</v>
+      </c>
+      <c r="H51" s="49" t="n">
+        <v>110</v>
+      </c>
+      <c r="I51" s="49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J51" s="49" t="inlineStr">
+        <is>
+          <t>https://cometps.com/</t>
+        </is>
+      </c>
+      <c r="K51" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E51" s="50" t="inlineStr">
-        <is>
-          <t>(844) 225-6243</t>
-        </is>
-      </c>
-      <c r="F51" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G51" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="H51" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="I51" s="49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J51" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="K51" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="L51" s="49" t="inlineStr">
         <is>
           <t>New</t>
@@ -3900,7 +3880,7 @@
       </c>
       <c r="M51" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the current owner. Blue Book-adjacent listing for janitorial/building cleaning. Verify city, legal name, and website on the call.</t>
+          <t>Business line: ask for Richard Basile and confirm current ownership. Marin commercial contract cleaning since ~1983. 21 Commercial Blvd, Ste 12. About 110 employees per BBB. Toll-free (800) 339-1035.</t>
         </is>
       </c>
       <c r="N51" s="49" t="inlineStr">
@@ -3927,7 +3907,7 @@
       </c>
       <c r="C52" s="49" t="inlineStr">
         <is>
-          <t>Los Gatos / South Bay, CA</t>
+          <t>San Jose, CA (Santa Clara)</t>
         </is>
       </c>
       <c r="D52" s="49" t="inlineStr">
@@ -3937,24 +3917,24 @@
       </c>
       <c r="E52" s="50" t="inlineStr">
         <is>
+          <t>(408) 625-7028</t>
+        </is>
+      </c>
+      <c r="F52" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G52" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="F52" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G52" s="49" t="inlineStr">
+      <c r="H52" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="H52" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="I52" s="49" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3967,7 +3947,7 @@
       </c>
       <c r="K52" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>abm@abmclean.com</t>
         </is>
       </c>
       <c r="L52" s="49" t="inlineStr">
@@ -3977,7 +3957,7 @@
       </c>
       <c r="M52" s="49" t="inlineStr">
         <is>
-          <t>Ask for the current owner. Site advertises janitorial, landscaping, and facility maintenance (Los Gatos museum testimonial). Verify phone, legal entity, and HQ city — a similarly named Sacramento firm also exists.</t>
+          <t>Business line: ask for the current owner. Janitorial plus landscaping and facility maintenance. Confirm this San Jose operator versus similarly named out-of-area firms.</t>
         </is>
       </c>
       <c r="N52" s="49" t="inlineStr">
@@ -3994,7 +3974,7 @@
     <row r="53" ht="48" customHeight="1" s="47">
       <c r="A53" s="49" t="inlineStr">
         <is>
-          <t>Signature Facilities Services</t>
+          <t>Premier Janitorial SF (House Cleaning SF, LLC)</t>
         </is>
       </c>
       <c r="B53" s="49" t="inlineStr">
@@ -4004,34 +3984,32 @@
       </c>
       <c r="C53" s="49" t="inlineStr">
         <is>
-          <t>Fremont, CA (Alameda)</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D53" s="49" t="inlineStr">
         <is>
+          <t>Noe Silva</t>
+        </is>
+      </c>
+      <c r="E53" s="50" t="inlineStr">
+        <is>
+          <t>(415) 742-1910</t>
+        </is>
+      </c>
+      <c r="F53" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G53" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="H53" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E53" s="50" t="inlineStr">
-        <is>
-          <t>(866) 943-4588</t>
-        </is>
-      </c>
-      <c r="F53" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G53" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="H53" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="I53" s="49" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -4039,12 +4017,12 @@
       </c>
       <c r="J53" s="49" t="inlineStr">
         <is>
-          <t>https://signaturefacilities.com/</t>
+          <t>https://housecleaningsf.com/</t>
         </is>
       </c>
       <c r="K53" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>info@housecleaningsf.com</t>
         </is>
       </c>
       <c r="L53" s="49" t="inlineStr">
@@ -4054,7 +4032,7 @@
       </c>
       <c r="M53" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the local principal. Public listings describe integrated janitorial/facilities work in Fremont. Confirm whether this is an independent Bay Area shop versus a national brand office.</t>
+          <t>Business line: ask for Noe Silva and confirm current ownership. Diamond Certified commercial janitorial division. Distinct from Premier Commercial Cleaning Solutions on the prior list.</t>
         </is>
       </c>
       <c r="N53" s="49" t="inlineStr">
@@ -4071,7 +4049,7 @@
     <row r="54" ht="48" customHeight="1" s="47">
       <c r="A54" s="49" t="inlineStr">
         <is>
-          <t>Jani-King of the San Francisco Bay Area</t>
+          <t>Enviro-Master of North Bay</t>
         </is>
       </c>
       <c r="B54" s="49" t="inlineStr">
@@ -4081,49 +4059,49 @@
       </c>
       <c r="C54" s="49" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA</t>
+          <t>Novato, CA (Marin)</t>
         </is>
       </c>
       <c r="D54" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified (regional franchise)</t>
+          <t>Ash Gorringe (Owner)</t>
         </is>
       </c>
       <c r="E54" s="50" t="inlineStr">
         <is>
+          <t>(415) 200-2638</t>
+        </is>
+      </c>
+      <c r="F54" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G54" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="F54" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G54" s="49" t="inlineStr">
+      <c r="H54" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="H54" s="49" t="inlineStr">
+      <c r="I54" s="49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J54" s="49" t="inlineStr">
+        <is>
+          <t>https://california.enviro-master.com/commercial-cleaning-locations/north-bay/</t>
+        </is>
+      </c>
+      <c r="K54" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="I54" s="49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J54" s="49" t="inlineStr">
-        <is>
-          <t>https://www.janiking.com/</t>
-        </is>
-      </c>
-      <c r="K54" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="L54" s="49" t="inlineStr">
         <is>
           <t>New</t>
@@ -4131,7 +4109,7 @@
       </c>
       <c r="M54" s="49" t="inlineStr">
         <is>
-          <t>Ask for the regional/franchise owner. National commercial-cleaning franchise with Bay Area operators. Verify local office phone, city, and owner on the call.</t>
+          <t>Business line: ask for Ash Gorringe and confirm current ownership. North Bay franchise for restroom/hygiene, janitorial supplies, windows, and commercial cleaning. 74 Digital Dr.</t>
         </is>
       </c>
       <c r="N54" s="49" t="inlineStr">
@@ -4225,7 +4203,7 @@
     <row r="56" ht="48" customHeight="1" s="47">
       <c r="A56" s="49" t="inlineStr">
         <is>
-          <t>Building Maintenance Solutions, Inc.</t>
+          <t>Alford Janitorial Services, LLC</t>
         </is>
       </c>
       <c r="B56" s="49" t="inlineStr">
@@ -4235,7 +4213,7 @@
       </c>
       <c r="C56" s="49" t="inlineStr">
         <is>
-          <t>Pittsburg, CA (Contra Costa)</t>
+          <t>Concord, CA (Contra Costa)</t>
         </is>
       </c>
       <c r="D56" s="49" t="inlineStr">
@@ -4245,37 +4223,37 @@
       </c>
       <c r="E56" s="50" t="inlineStr">
         <is>
+          <t>(510) 943-8752</t>
+        </is>
+      </c>
+      <c r="F56" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G56" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="F56" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G56" s="49" t="inlineStr">
+      <c r="H56" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="H56" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="I56" s="49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J56" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>https://alfordjanitorial.com/</t>
         </is>
       </c>
       <c r="K56" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>info@alfordjanitorial.com</t>
         </is>
       </c>
       <c r="L56" s="49" t="inlineStr">
@@ -4285,7 +4263,7 @@
       </c>
       <c r="M56" s="49" t="inlineStr">
         <is>
-          <t>Ask for the current owner. Public directories list a Pittsburg-area commercial janitorial firm. Verify phone, website, and ownership on the call.</t>
+          <t>Business line: ask for the current owner. Family-owned East Bay commercial janitorial for offices, schools, churches, clinics, gyms, and retail. 1265 Pine Creek Wy.</t>
         </is>
       </c>
       <c r="N56" s="49" t="inlineStr">
@@ -4302,7 +4280,7 @@
     <row r="57" ht="48" customHeight="1" s="47">
       <c r="A57" s="49" t="inlineStr">
         <is>
-          <t>Classic Janitorial Service</t>
+          <t>GDL Building Maintenance</t>
         </is>
       </c>
       <c r="B57" s="49" t="inlineStr">
@@ -4312,7 +4290,7 @@
       </c>
       <c r="C57" s="49" t="inlineStr">
         <is>
-          <t>Hayward, CA (Alameda)</t>
+          <t>Cotati, CA (Sonoma)</t>
         </is>
       </c>
       <c r="D57" s="49" t="inlineStr">
@@ -4322,37 +4300,37 @@
       </c>
       <c r="E57" s="50" t="inlineStr">
         <is>
+          <t>(707) 242-6922</t>
+        </is>
+      </c>
+      <c r="F57" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G57" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="F57" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G57" s="49" t="inlineStr">
+      <c r="H57" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="H57" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="I57" s="49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J57" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>https://gdlserves.com/</t>
         </is>
       </c>
       <c r="K57" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>customercare@gdlserves.com</t>
         </is>
       </c>
       <c r="L57" s="49" t="inlineStr">
@@ -4362,7 +4340,7 @@
       </c>
       <c r="M57" s="49" t="inlineStr">
         <is>
-          <t>Ask for the current owner. Appears in Hayward cleaning-service directories. Verify legal name, phone, and commercial vs residential mix on the call.</t>
+          <t>Business line: ask for the current owner. North Bay commercial-only janitorial, carpet, floor waxing, windows, and post-construction. 321 Blodgett St, Ste A.</t>
         </is>
       </c>
       <c r="N57" s="49" t="inlineStr">
@@ -4379,7 +4357,7 @@
     <row r="58" ht="48" customHeight="1" s="47">
       <c r="A58" s="49" t="inlineStr">
         <is>
-          <t>Resourceful Janitorial and Business Solutions</t>
+          <t>Nico Janitorial</t>
         </is>
       </c>
       <c r="B58" s="49" t="inlineStr">
@@ -4389,7 +4367,7 @@
       </c>
       <c r="C58" s="49" t="inlineStr">
         <is>
-          <t>Hayward, CA (Alameda)</t>
+          <t>San Leandro, CA (Alameda)</t>
         </is>
       </c>
       <c r="D58" s="49" t="inlineStr">
@@ -4399,37 +4377,37 @@
       </c>
       <c r="E58" s="50" t="inlineStr">
         <is>
+          <t>(510) 844-4638</t>
+        </is>
+      </c>
+      <c r="F58" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G58" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="F58" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G58" s="49" t="inlineStr">
+      <c r="H58" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="H58" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="I58" s="49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J58" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>https://www.nicojanitorial.com/</t>
         </is>
       </c>
       <c r="K58" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>info@nicojanitorial.com</t>
         </is>
       </c>
       <c r="L58" s="49" t="inlineStr">
@@ -4439,7 +4417,7 @@
       </c>
       <c r="M58" s="49" t="inlineStr">
         <is>
-          <t>Ask for the current owner. Listed among Hayward commercial cleaning providers. Verify phone, website, and current operating status on the call.</t>
+          <t>Business line: ask for the current owner. East Bay commercial janitorial for offices, healthcare, schools, manufacturing, and hospitality. 933 MacArthur Blvd, Ste 1B. CA DIR JS-LR-1001308309.</t>
         </is>
       </c>
       <c r="N58" s="49" t="inlineStr">
@@ -4456,7 +4434,7 @@
     <row r="59" ht="48" customHeight="1" s="47">
       <c r="A59" s="49" t="inlineStr">
         <is>
-          <t>Peninsula Mobile Service</t>
+          <t>JLP Building Maintenance, LLC</t>
         </is>
       </c>
       <c r="B59" s="49" t="inlineStr">
@@ -4466,47 +4444,45 @@
       </c>
       <c r="C59" s="49" t="inlineStr">
         <is>
-          <t>San Mateo County, CA</t>
+          <t>Fremont, CA (Alameda)</t>
         </is>
       </c>
       <c r="D59" s="49" t="inlineStr">
         <is>
+          <t>Jorge (first name in client testimonials; surname not independently verified)</t>
+        </is>
+      </c>
+      <c r="E59" s="50" t="inlineStr">
+        <is>
+          <t>(510) 656-8300</t>
+        </is>
+      </c>
+      <c r="F59" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G59" s="49" t="n">
+        <v>20</v>
+      </c>
+      <c r="H59" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E59" s="50" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="F59" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G59" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="H59" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="I59" s="49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J59" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>http://www.jlpbuilding.com/</t>
         </is>
       </c>
       <c r="K59" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>info@jlpbuilding.com</t>
         </is>
       </c>
       <c r="L59" s="49" t="inlineStr">
@@ -4516,7 +4492,7 @@
       </c>
       <c r="M59" s="49" t="inlineStr">
         <is>
-          <t>Ask for the current owner. Blue Book-adjacent Peninsula building-maintenance listing. Verify commercial janitorial fit, phone, and city on the call.</t>
+          <t>Business line: ask for Jorge and confirm current ownership. East Bay/South Bay janitorial, windows, carpet, and clean-room/ESD floor care. 48834 Kato Rd, Ste 109A. Distinct from Fremont Janitorial on the prior list.</t>
         </is>
       </c>
       <c r="N59" s="49" t="inlineStr">
@@ -4533,7 +4509,7 @@
     <row r="60" ht="48" customHeight="1" s="47">
       <c r="A60" s="49" t="inlineStr">
         <is>
-          <t>Maintenance Professionals, Inc.</t>
+          <t>Extreme Janitors</t>
         </is>
       </c>
       <c r="B60" s="49" t="inlineStr">
@@ -4543,49 +4519,45 @@
       </c>
       <c r="C60" s="49" t="inlineStr">
         <is>
-          <t>San Jose / South Bay, CA</t>
+          <t>Oakland, CA (Alameda)</t>
         </is>
       </c>
       <c r="D60" s="49" t="inlineStr">
         <is>
+          <t>Abel Casanga (Founder)</t>
+        </is>
+      </c>
+      <c r="E60" s="50" t="inlineStr">
+        <is>
+          <t>(510) 842-8949</t>
+        </is>
+      </c>
+      <c r="F60" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G60" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="H60" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="I60" s="49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J60" s="49" t="inlineStr">
+        <is>
+          <t>https://extremejanitors.com/</t>
+        </is>
+      </c>
+      <c r="K60" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E60" s="50" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="F60" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G60" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="H60" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="I60" s="49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J60" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="K60" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="L60" s="49" t="inlineStr">
         <is>
           <t>New</t>
@@ -4593,7 +4565,7 @@
       </c>
       <c r="M60" s="49" t="inlineStr">
         <is>
-          <t>Ask for the current owner. Blue Book-adjacent South Bay janitorial/building-maintenance listing. Verify phone, website, and ownership on the call.</t>
+          <t>Business line: ask for Abel Casanga and confirm current ownership. Oakland family-owned commercial janitorial since 2015. 2872 E 7th St.</t>
         </is>
       </c>
       <c r="N60" s="49" t="inlineStr">
@@ -4610,7 +4582,7 @@
     <row r="61" ht="48" customHeight="1" s="47">
       <c r="A61" s="49" t="inlineStr">
         <is>
-          <t>Lua's Construction &amp; Facilities</t>
+          <t>KD Janitorial Services, Inc.</t>
         </is>
       </c>
       <c r="B61" s="49" t="inlineStr">
@@ -4620,17 +4592,17 @@
       </c>
       <c r="C61" s="49" t="inlineStr">
         <is>
-          <t>San Jose, CA (Santa Clara)</t>
+          <t>Oakland, CA (Alameda); also serves SF and San Jose</t>
         </is>
       </c>
       <c r="D61" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>Kelvin Diaz (Founder/CEO)</t>
         </is>
       </c>
       <c r="E61" s="50" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>(510) 422-3260</t>
         </is>
       </c>
       <c r="F61" s="49" t="inlineStr">
@@ -4638,29 +4610,25 @@
           <t>Business Line</t>
         </is>
       </c>
-      <c r="G61" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="H61" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
+      <c r="G61" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="H61" s="49" t="n">
+        <v>10</v>
       </c>
       <c r="I61" s="49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J61" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>https://kdjanitorial.com/</t>
         </is>
       </c>
       <c r="K61" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>info@kdjanitorial.com</t>
         </is>
       </c>
       <c r="L61" s="49" t="inlineStr">
@@ -4670,7 +4638,7 @@
       </c>
       <c r="M61" s="49" t="inlineStr">
         <is>
-          <t>Ask for the current owner. Blue Book listing for janitorial and parking-lot maintenance. Verify phone, commercial mix, and current operating status on the call.</t>
+          <t>Business line: ask for Kelvin Diaz and confirm current ownership. Family-owned commercial/industrial cleaning since 2017. LinkedIn HQ Oakland; some materials also list Tracy (outside the nine counties).</t>
         </is>
       </c>
       <c r="N61" s="49" t="inlineStr">
@@ -4839,7 +4807,7 @@
     <row r="64" ht="48" customHeight="1" s="47">
       <c r="A64" s="49" t="inlineStr">
         <is>
-          <t>Sta-Clean</t>
+          <t>Sta-Clean Services, Inc.</t>
         </is>
       </c>
       <c r="B64" s="49" t="inlineStr">
@@ -4854,7 +4822,7 @@
       </c>
       <c r="D64" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>Brant (owner first name published; surname not independently verified)</t>
         </is>
       </c>
       <c r="E64" s="50" t="inlineStr">
@@ -4897,7 +4865,7 @@
       </c>
       <c r="M64" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the current owner. Commercial/office janitorial since 1981 for SF, Marin, Sonoma, and Contra Costa offices, schools, health clubs, and warehouses.</t>
+          <t>Business line: ask for Brant and confirm current ownership. Commercial/office janitorial since 1981 for SF, Marin, Sonoma, and Contra Costa.</t>
         </is>
       </c>
       <c r="N64" s="49" t="inlineStr">
@@ -4914,7 +4882,7 @@
     <row r="65" ht="48" customHeight="1" s="47">
       <c r="A65" s="49" t="inlineStr">
         <is>
-          <t>Consolidated Cleaning Solutions Inc.</t>
+          <t>Consolidated Cleaning Solutions, Inc.</t>
         </is>
       </c>
       <c r="B65" s="49" t="inlineStr">
@@ -4929,44 +4897,42 @@
       </c>
       <c r="D65" s="49" t="inlineStr">
         <is>
+          <t>Martin Gonzalez</t>
+        </is>
+      </c>
+      <c r="E65" s="50" t="inlineStr">
+        <is>
+          <t>(510) 969-7416</t>
+        </is>
+      </c>
+      <c r="F65" s="49" t="inlineStr">
+        <is>
+          <t>Business Line</t>
+        </is>
+      </c>
+      <c r="G65" s="49" t="n">
+        <v>42</v>
+      </c>
+      <c r="H65" s="49" t="inlineStr">
+        <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="E65" s="50" t="inlineStr">
-        <is>
-          <t>(510) 969-7416</t>
-        </is>
-      </c>
-      <c r="F65" s="49" t="inlineStr">
-        <is>
-          <t>Business Line</t>
-        </is>
-      </c>
-      <c r="G65" s="49" t="inlineStr">
+      <c r="I65" s="49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J65" s="49" t="inlineStr">
+        <is>
+          <t>https://consolidated-cleaning.com/</t>
+        </is>
+      </c>
+      <c r="K65" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="H65" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="I65" s="49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J65" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
-      <c r="K65" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="L65" s="49" t="inlineStr">
         <is>
           <t>New</t>
@@ -4974,7 +4940,7 @@
       </c>
       <c r="M65" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the current owner. Public listings place the firm at 406 Pendleton Way, Oakland. Verify website, legal status, and commercial janitorial mix on the call.</t>
+          <t>Business line: ask for Martin Gonzalez and confirm current ownership. Minority-owned commercial janitorial since 1984; windows, carpet, pressure washing, and construction cleaning.</t>
         </is>
       </c>
       <c r="N65" s="49" t="inlineStr">
@@ -4991,7 +4957,7 @@
     <row r="66" ht="48" customHeight="1" s="47">
       <c r="A66" s="49" t="inlineStr">
         <is>
-          <t>American Empire Building Services</t>
+          <t>Global Maintenance Resources</t>
         </is>
       </c>
       <c r="B66" s="49" t="inlineStr">
@@ -5001,7 +4967,7 @@
       </c>
       <c r="C66" s="49" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Union City, CA (Alameda)</t>
         </is>
       </c>
       <c r="D66" s="49" t="inlineStr">
@@ -5011,7 +4977,7 @@
       </c>
       <c r="E66" s="50" t="inlineStr">
         <is>
-          <t>(415) 536-7842</t>
+          <t>(510) 377-6085</t>
         </is>
       </c>
       <c r="F66" s="49" t="inlineStr">
@@ -5019,29 +4985,27 @@
           <t>Business Line</t>
         </is>
       </c>
-      <c r="G66" s="49" t="inlineStr">
+      <c r="G66" s="49" t="n">
+        <v>25</v>
+      </c>
+      <c r="H66" s="49" t="inlineStr">
         <is>
           <t>Not publicly verified</t>
         </is>
       </c>
-      <c r="H66" s="49" t="inlineStr">
-        <is>
-          <t>Not publicly verified</t>
-        </is>
-      </c>
       <c r="I66" s="49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J66" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>http://gmresources.com/</t>
         </is>
       </c>
       <c r="K66" s="49" t="inlineStr">
         <is>
-          <t>Not publicly verified</t>
+          <t>info@GMResources.com</t>
         </is>
       </c>
       <c r="L66" s="49" t="inlineStr">
@@ -5051,7 +5015,7 @@
       </c>
       <c r="M66" s="49" t="inlineStr">
         <is>
-          <t>Business line: ask for the current owner. Public listings place the firm at 440 Bryant St, San Francisco. Verify website and current operating status on the call.</t>
+          <t>Business line: ask for the current owner. Commercial janitorial and building maintenance since 2001. 1684 Decoto Rd #314. Offices, community centers, fitness, and HOA common areas.</t>
         </is>
       </c>
       <c r="N66" s="49" t="inlineStr">
